--- a/data.mn/public/datasets/industrial-output-total-monthly.xlsx
+++ b/data.mn/public/datasets/industrial-output-total-monthly.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5095.5</v>
+        <v>5297.3</v>
       </c>
     </row>
     <row r="103">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>5211.1</v>
+        <v>5330.5</v>
       </c>
     </row>
     <row r="104">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5848.3</v>
+        <v>5851.3</v>
       </c>
     </row>
     <row r="105">
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5570.2</v>
+        <v>5783.8</v>
       </c>
     </row>
     <row r="106">
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>6597.9</v>
+        <v>6598.8</v>
       </c>
     </row>
     <row r="107">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>6994.6</v>
+        <v>6999.3</v>
       </c>
     </row>
     <row r="108">
@@ -1500,7 +1500,27 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>7007.5</v>
+        <v>7062.3</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>6856.3</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>7233.7</v>
       </c>
     </row>
   </sheetData>
@@ -1514,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2540,7 +2560,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5095.5</v>
+        <v>5297.3</v>
       </c>
     </row>
     <row r="103">
@@ -2550,7 +2570,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>5211.1</v>
+        <v>5330.5</v>
       </c>
     </row>
     <row r="104">
@@ -2560,7 +2580,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5848.3</v>
+        <v>5851.3</v>
       </c>
     </row>
     <row r="105">
@@ -2570,7 +2590,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5570.2</v>
+        <v>5783.8</v>
       </c>
     </row>
     <row r="106">
@@ -2580,7 +2600,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>6597.9</v>
+        <v>6598.8</v>
       </c>
     </row>
     <row r="107">
@@ -2590,7 +2610,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>6994.6</v>
+        <v>6999.3</v>
       </c>
     </row>
     <row r="108">
@@ -2600,7 +2620,27 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>7007.5</v>
+        <v>7062.3</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>6856.3</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>7233.7</v>
       </c>
     </row>
   </sheetData>
